--- a/data/exploration/training_data/description_training_sample_41.xlsx
+++ b/data/exploration/training_data/description_training_sample_41.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\data\exploration\training_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE25E7-D261-4EE0-89A0-90599F9A1E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899CCB8D-FDE2-4175-9AFD-81F862EFACED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="595">
   <si>
     <t>video_id</t>
   </si>
@@ -4196,6 +4196,12 @@
   <si>
     <t>politics_title_desc</t>
   </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>politics_final_manual</t>
+  </si>
 </sst>
 </file>
 
@@ -4245,7 +4251,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4256,6 +4281,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5077F2DC-8FD6-40E6-8E44-5A408B2B5F78}" name="Table2" displayName="Table2" ref="A1:G201" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:G201" xr:uid="{5077F2DC-8FD6-40E6-8E44-5A408B2B5F78}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E1E913B2-11B8-4375-A7AC-94722024C3FD}" name="video_id"/>
+    <tableColumn id="2" xr3:uid="{E733C26F-1CAB-42AD-BB26-5CDB78C21A72}" name="title"/>
+    <tableColumn id="3" xr3:uid="{FA272B72-079B-420D-A50E-393213BF5D28}" name="description"/>
+    <tableColumn id="4" xr3:uid="{8EFD6A3D-11B0-45E9-8A74-BF46A65A90DE}" name="politics_title"/>
+    <tableColumn id="5" xr3:uid="{C5872EB8-274F-4FEA-9D3A-DF5049F484EA}" name="politics_title_desc"/>
+    <tableColumn id="6" xr3:uid="{B9191C54-E78E-4E0A-9148-CD5F7DFF52A2}" name="politics_final_manual"/>
+    <tableColumn id="7" xr3:uid="{1C3FE082-053B-45E3-B610-ACA9040FD790}" name="index"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4543,15 +4584,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="2" max="2" width="94.21875" customWidth="1"/>
-    <col min="3" max="3" width="2.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4567,8 +4611,14 @@
       <c r="E1" s="1" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4581,8 +4631,11 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4595,8 +4648,11 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4609,8 +4665,14 @@
       <c r="D4">
         <v>-1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4623,8 +4685,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4637,8 +4702,11 @@
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4651,8 +4719,14 @@
       <c r="D7">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4665,8 +4739,11 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4679,8 +4756,11 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -4693,8 +4773,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -4707,8 +4790,11 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -4721,8 +4807,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -4735,8 +4824,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -4749,8 +4841,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -4763,8 +4858,11 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -4777,8 +4875,11 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -4791,8 +4892,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -4805,8 +4909,11 @@
       <c r="D18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -4819,8 +4926,11 @@
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -4833,8 +4943,11 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -4847,8 +4960,11 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4861,8 +4977,11 @@
       <c r="D22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -4875,8 +4994,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -4889,8 +5011,11 @@
       <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -4903,8 +5028,11 @@
       <c r="D25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -4917,8 +5045,11 @@
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -4931,8 +5062,11 @@
       <c r="D27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5079,11 @@
       <c r="D28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -4959,8 +5096,11 @@
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -4973,8 +5113,11 @@
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -4987,8 +5130,11 @@
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -5001,8 +5147,11 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -5015,8 +5164,11 @@
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -5029,8 +5181,11 @@
       <c r="D34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -5043,8 +5198,11 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -5057,8 +5215,11 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -5071,8 +5232,11 @@
       <c r="D37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -5085,8 +5249,11 @@
       <c r="D38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -5099,8 +5266,11 @@
       <c r="D39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -5113,8 +5283,11 @@
       <c r="D40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -5127,8 +5300,11 @@
       <c r="D41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -5141,8 +5317,11 @@
       <c r="D42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -5152,8 +5331,11 @@
       <c r="D43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -5166,8 +5348,11 @@
       <c r="D44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -5180,8 +5365,11 @@
       <c r="D45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -5194,8 +5382,11 @@
       <c r="D46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -5208,8 +5399,11 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -5222,8 +5416,11 @@
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>143</v>
       </c>
@@ -5236,8 +5433,11 @@
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>146</v>
       </c>
@@ -5250,8 +5450,11 @@
       <c r="D50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>149</v>
       </c>
@@ -5264,8 +5467,11 @@
       <c r="D51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>152</v>
       </c>
@@ -5276,10 +5482,16 @@
         <v>154</v>
       </c>
       <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>155</v>
       </c>
@@ -5292,8 +5504,14 @@
       <c r="D53">
         <v>-1</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53">
+        <v>-1</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>158</v>
       </c>
@@ -5306,8 +5524,11 @@
       <c r="D54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -5318,10 +5539,13 @@
         <v>163</v>
       </c>
       <c r="D55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>164</v>
       </c>
@@ -5334,8 +5558,11 @@
       <c r="D56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -5348,8 +5575,11 @@
       <c r="D57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -5359,8 +5589,11 @@
       <c r="D58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>172</v>
       </c>
@@ -5373,8 +5606,14 @@
       <c r="D59">
         <v>-1</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -5387,8 +5626,11 @@
       <c r="D60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>177</v>
       </c>
@@ -5401,8 +5643,11 @@
       <c r="D61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>180</v>
       </c>
@@ -5415,8 +5660,11 @@
       <c r="D62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>183</v>
       </c>
@@ -5429,8 +5677,11 @@
       <c r="D63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>186</v>
       </c>
@@ -5443,8 +5694,11 @@
       <c r="D64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>189</v>
       </c>
@@ -5455,10 +5709,13 @@
         <v>191</v>
       </c>
       <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>192</v>
       </c>
@@ -5471,8 +5728,11 @@
       <c r="D66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>195</v>
       </c>
@@ -5485,8 +5745,11 @@
       <c r="D67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>198</v>
       </c>
@@ -5499,8 +5762,14 @@
       <c r="D68">
         <v>-1</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>201</v>
       </c>
@@ -5513,8 +5782,11 @@
       <c r="D69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>204</v>
       </c>
@@ -5527,8 +5799,11 @@
       <c r="D70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>207</v>
       </c>
@@ -5541,8 +5816,11 @@
       <c r="D71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>210</v>
       </c>
@@ -5555,8 +5833,11 @@
       <c r="D72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>213</v>
       </c>
@@ -5569,8 +5850,11 @@
       <c r="D73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>216</v>
       </c>
@@ -5583,8 +5867,11 @@
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>219</v>
       </c>
@@ -5597,8 +5884,11 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>222</v>
       </c>
@@ -5611,8 +5901,11 @@
       <c r="D76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>225</v>
       </c>
@@ -5625,8 +5918,11 @@
       <c r="D77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>228</v>
       </c>
@@ -5639,8 +5935,11 @@
       <c r="D78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>231</v>
       </c>
@@ -5653,8 +5952,11 @@
       <c r="D79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>234</v>
       </c>
@@ -5664,8 +5966,17 @@
       <c r="C80" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80">
+        <v>-1</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>237</v>
       </c>
@@ -5675,8 +5986,14 @@
       <c r="C81" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -5686,8 +6003,14 @@
       <c r="C82" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>243</v>
       </c>
@@ -5697,8 +6020,14 @@
       <c r="C83" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>246</v>
       </c>
@@ -5708,8 +6037,14 @@
       <c r="C84" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>249</v>
       </c>
@@ -5719,8 +6054,14 @@
       <c r="C85" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>252</v>
       </c>
@@ -5730,8 +6071,14 @@
       <c r="C86" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>255</v>
       </c>
@@ -5741,8 +6088,14 @@
       <c r="C87" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>258</v>
       </c>
@@ -5752,8 +6105,14 @@
       <c r="C88" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>261</v>
       </c>
@@ -5763,8 +6122,14 @@
       <c r="C89" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>264</v>
       </c>
@@ -5774,8 +6139,14 @@
       <c r="C90" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>267</v>
       </c>
@@ -5785,8 +6156,17 @@
       <c r="C91" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91">
+        <v>-1</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>270</v>
       </c>
@@ -5796,8 +6176,14 @@
       <c r="C92" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>273</v>
       </c>
@@ -5807,8 +6193,14 @@
       <c r="C93" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>276</v>
       </c>
@@ -5818,8 +6210,14 @@
       <c r="C94" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>279</v>
       </c>
@@ -5829,8 +6227,14 @@
       <c r="C95" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>282</v>
       </c>
@@ -5840,8 +6244,14 @@
       <c r="C96" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>285</v>
       </c>
@@ -5851,8 +6261,14 @@
       <c r="C97" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>288</v>
       </c>
@@ -5862,8 +6278,14 @@
       <c r="C98" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>291</v>
       </c>
@@ -5873,8 +6295,17 @@
       <c r="C99" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99">
+        <v>-1</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>294</v>
       </c>
@@ -5884,16 +6315,28 @@
       <c r="C100" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>297</v>
       </c>
       <c r="B101" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>299</v>
       </c>
@@ -5903,8 +6346,17 @@
       <c r="C102" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102">
+        <v>-1</v>
+      </c>
+      <c r="E102">
+        <v>-1</v>
+      </c>
+      <c r="G102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>301</v>
       </c>
@@ -5914,8 +6366,17 @@
       <c r="C103" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103">
+        <v>-1</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>304</v>
       </c>
@@ -5925,8 +6386,14 @@
       <c r="C104" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>307</v>
       </c>
@@ -5936,8 +6403,14 @@
       <c r="C105" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>310</v>
       </c>
@@ -5947,16 +6420,31 @@
       <c r="C106" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>313</v>
       </c>
       <c r="B107" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107">
+        <v>-1</v>
+      </c>
+      <c r="E107">
+        <v>-1</v>
+      </c>
+      <c r="G107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>315</v>
       </c>
@@ -5966,8 +6454,14 @@
       <c r="C108" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>318</v>
       </c>
@@ -5977,8 +6471,14 @@
       <c r="C109" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>321</v>
       </c>
@@ -5988,8 +6488,14 @@
       <c r="C110" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>324</v>
       </c>
@@ -5999,8 +6505,14 @@
       <c r="C111" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>327</v>
       </c>
@@ -6010,8 +6522,14 @@
       <c r="C112" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>330</v>
       </c>
@@ -6021,8 +6539,14 @@
       <c r="C113" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>332</v>
       </c>
@@ -6032,8 +6556,14 @@
       <c r="C114" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>335</v>
       </c>
@@ -6043,8 +6573,14 @@
       <c r="C115" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>337</v>
       </c>
@@ -6054,8 +6590,14 @@
       <c r="C116" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>340</v>
       </c>
@@ -6065,8 +6607,14 @@
       <c r="C117" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>343</v>
       </c>
@@ -6076,8 +6624,14 @@
       <c r="C118" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>346</v>
       </c>
@@ -6087,8 +6641,14 @@
       <c r="C119" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -6098,8 +6658,17 @@
       <c r="C120" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D120">
+        <v>-1</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>352</v>
       </c>
@@ -6109,8 +6678,14 @@
       <c r="C121" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>355</v>
       </c>
@@ -6120,8 +6695,14 @@
       <c r="C122" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>358</v>
       </c>
@@ -6131,8 +6712,14 @@
       <c r="C123" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>361</v>
       </c>
@@ -6142,8 +6729,14 @@
       <c r="C124" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>364</v>
       </c>
@@ -6153,8 +6746,14 @@
       <c r="C125" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>367</v>
       </c>
@@ -6164,8 +6763,14 @@
       <c r="C126" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>370</v>
       </c>
@@ -6175,8 +6780,17 @@
       <c r="C127" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D127">
+        <v>-1</v>
+      </c>
+      <c r="E127">
+        <v>-1</v>
+      </c>
+      <c r="G127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>373</v>
       </c>
@@ -6186,8 +6800,14 @@
       <c r="C128" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>376</v>
       </c>
@@ -6197,8 +6817,14 @@
       <c r="C129" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>379</v>
       </c>
@@ -6208,8 +6834,14 @@
       <c r="C130" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>382</v>
       </c>
@@ -6219,8 +6851,14 @@
       <c r="C131" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>385</v>
       </c>
@@ -6230,8 +6868,14 @@
       <c r="C132" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>388</v>
       </c>
@@ -6241,8 +6885,14 @@
       <c r="C133" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>391</v>
       </c>
@@ -6252,8 +6902,17 @@
       <c r="C134" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D134">
+        <v>-1</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>394</v>
       </c>
@@ -6263,8 +6922,14 @@
       <c r="C135" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>397</v>
       </c>
@@ -6274,8 +6939,14 @@
       <c r="C136" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>400</v>
       </c>
@@ -6285,8 +6956,14 @@
       <c r="C137" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="G137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>403</v>
       </c>
@@ -6296,8 +6973,17 @@
       <c r="C138" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D138">
+        <v>-1</v>
+      </c>
+      <c r="E138">
+        <v>-1</v>
+      </c>
+      <c r="G138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>406</v>
       </c>
@@ -6307,8 +6993,17 @@
       <c r="C139" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D139">
+        <v>-1</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>409</v>
       </c>
@@ -6318,8 +7013,14 @@
       <c r="C140" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>412</v>
       </c>
@@ -6329,8 +7030,14 @@
       <c r="C141" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>415</v>
       </c>
@@ -6340,8 +7047,14 @@
       <c r="C142" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>418</v>
       </c>
@@ -6351,8 +7064,14 @@
       <c r="C143" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>421</v>
       </c>
@@ -6362,8 +7081,14 @@
       <c r="C144" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>424</v>
       </c>
@@ -6373,16 +7098,31 @@
       <c r="C145" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>427</v>
       </c>
       <c r="B146" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D146">
+        <v>-1</v>
+      </c>
+      <c r="E146">
+        <v>-1</v>
+      </c>
+      <c r="G146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>429</v>
       </c>
@@ -6392,8 +7132,14 @@
       <c r="C147" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>432</v>
       </c>
@@ -6403,8 +7149,14 @@
       <c r="C148" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>435</v>
       </c>
@@ -6414,8 +7166,14 @@
       <c r="C149" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>438</v>
       </c>
@@ -6425,8 +7183,14 @@
       <c r="C150" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>441</v>
       </c>
@@ -6436,24 +7200,42 @@
       <c r="C151" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>444</v>
       </c>
       <c r="B152" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>446</v>
       </c>
       <c r="B153" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>448</v>
       </c>
@@ -6463,8 +7245,14 @@
       <c r="C154" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>451</v>
       </c>
@@ -6474,8 +7262,14 @@
       <c r="C155" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>454</v>
       </c>
@@ -6485,8 +7279,14 @@
       <c r="C156" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>457</v>
       </c>
@@ -6496,8 +7296,14 @@
       <c r="C157" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="G157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>460</v>
       </c>
@@ -6507,8 +7313,14 @@
       <c r="C158" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>463</v>
       </c>
@@ -6518,8 +7330,14 @@
       <c r="C159" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>466</v>
       </c>
@@ -6529,8 +7347,14 @@
       <c r="C160" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>469</v>
       </c>
@@ -6540,8 +7364,14 @@
       <c r="C161" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="G161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>472</v>
       </c>
@@ -6551,8 +7381,14 @@
       <c r="C162" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>475</v>
       </c>
@@ -6562,8 +7398,14 @@
       <c r="C163" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>478</v>
       </c>
@@ -6573,8 +7415,14 @@
       <c r="C164" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>481</v>
       </c>
@@ -6584,8 +7432,14 @@
       <c r="C165" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>484</v>
       </c>
@@ -6595,8 +7449,14 @@
       <c r="C166" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>487</v>
       </c>
@@ -6606,8 +7466,14 @@
       <c r="C167" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>490</v>
       </c>
@@ -6617,8 +7483,14 @@
       <c r="C168" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>493</v>
       </c>
@@ -6628,8 +7500,17 @@
       <c r="C169" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D169">
+        <v>-1</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>496</v>
       </c>
@@ -6639,8 +7520,14 @@
       <c r="C170" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>499</v>
       </c>
@@ -6650,8 +7537,14 @@
       <c r="C171" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>502</v>
       </c>
@@ -6661,8 +7554,14 @@
       <c r="C172" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>505</v>
       </c>
@@ -6672,8 +7571,14 @@
       <c r="C173" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>508</v>
       </c>
@@ -6683,8 +7588,17 @@
       <c r="C174" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D174">
+        <v>-1</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>511</v>
       </c>
@@ -6694,8 +7608,14 @@
       <c r="C175" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>514</v>
       </c>
@@ -6705,8 +7625,14 @@
       <c r="C176" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>517</v>
       </c>
@@ -6716,8 +7642,14 @@
       <c r="C177" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>520</v>
       </c>
@@ -6727,8 +7659,14 @@
       <c r="C178" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>523</v>
       </c>
@@ -6738,8 +7676,14 @@
       <c r="C179" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>526</v>
       </c>
@@ -6749,8 +7693,14 @@
       <c r="C180" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>529</v>
       </c>
@@ -6760,8 +7710,14 @@
       <c r="C181" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>532</v>
       </c>
@@ -6771,8 +7727,14 @@
       <c r="C182" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>535</v>
       </c>
@@ -6782,8 +7744,17 @@
       <c r="C183" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D183">
+        <v>-1</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>538</v>
       </c>
@@ -6793,8 +7764,17 @@
       <c r="C184" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D184">
+        <v>-1</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>541</v>
       </c>
@@ -6804,8 +7784,14 @@
       <c r="C185" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>544</v>
       </c>
@@ -6815,8 +7801,14 @@
       <c r="C186" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>547</v>
       </c>
@@ -6826,8 +7818,14 @@
       <c r="C187" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="G187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>550</v>
       </c>
@@ -6837,8 +7835,14 @@
       <c r="C188" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>553</v>
       </c>
@@ -6848,8 +7852,14 @@
       <c r="C189" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="G189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>556</v>
       </c>
@@ -6859,8 +7869,14 @@
       <c r="C190" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>559</v>
       </c>
@@ -6870,8 +7886,14 @@
       <c r="C191" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>562</v>
       </c>
@@ -6881,8 +7903,14 @@
       <c r="C192" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>565</v>
       </c>
@@ -6892,8 +7920,14 @@
       <c r="C193" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>568</v>
       </c>
@@ -6903,8 +7937,14 @@
       <c r="C194" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>571</v>
       </c>
@@ -6914,8 +7954,17 @@
       <c r="C195" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D195">
+        <v>-1</v>
+      </c>
+      <c r="E195">
+        <v>-1</v>
+      </c>
+      <c r="G195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>574</v>
       </c>
@@ -6925,8 +7974,17 @@
       <c r="C196" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D196">
+        <v>-1</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>577</v>
       </c>
@@ -6936,8 +7994,14 @@
       <c r="C197" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>580</v>
       </c>
@@ -6947,8 +8011,14 @@
       <c r="C198" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="G198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>583</v>
       </c>
@@ -6958,8 +8028,14 @@
       <c r="C199" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>586</v>
       </c>
@@ -6969,8 +8045,14 @@
       <c r="C200" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>589</v>
       </c>
@@ -6980,8 +8062,17 @@
       <c r="C201" t="s">
         <v>56</v>
       </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>